--- a/buildplan_generator/output/25-087 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-087 GENERATED BUILD PLAN.xlsx
@@ -74,12 +74,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
@@ -88,6 +82,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-058, 23-059, 23-060, 25-113, 25-010</t>
+          <t>25-039, 24-006, 25-042, 25-088, 25-085</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,15 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -673,12 +671,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -722,8 +720,8 @@
       <c r="E9" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>2.5</v>
+      <c r="F9" s="9" t="n">
+        <v>3.2</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -732,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>2.0-3.5</t>
+          <t>ratio=1.08 (0.88-1.50)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -759,8 +757,8 @@
       <c r="E10" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>5</v>
+      <c r="F10" s="9" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -769,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>3.0-6.0</t>
+          <t>ratio=1.17 (0.29-2.00)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -797,16 +795,16 @@
         <v>1</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>0.5-1.5</t>
+          <t>ratio=0.78 (n=2)</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -838,12 +836,12 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -875,12 +873,12 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -908,16 +906,16 @@
         <v>1</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.50 (n=2)</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -945,16 +943,16 @@
         <v>2</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>2.5-3.5</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -982,16 +980,16 @@
         <v>2</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>2.0-7.5</t>
+          <t>ratio=1.19 (n=2)</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1035,8 +1033,8 @@
       <c r="E18" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="F18" s="10" t="n">
-        <v>8</v>
+      <c r="F18" s="9" t="n">
+        <v>7</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1045,7 +1043,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>7.0-9.0</t>
+          <t>ratio=1.00 (0.60-1.10)</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1073,16 +1071,16 @@
         <v>3</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>global:0.8-39.0</t>
+          <t>ratio=0.75 (0.47-1.10)</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1126,8 +1124,8 @@
       <c r="E21" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F21" s="10" t="n">
-        <v>3</v>
+      <c r="F21" s="9" t="n">
+        <v>4.2</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1136,7 +1134,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>3.0-5.5</t>
+          <t>ratio=0.83 (0.58-1.10)</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1180,7 +1178,7 @@
       <c r="E23" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="F23" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -1190,7 +1188,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1234,17 +1232,17 @@
       <c r="E25" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="9" t="n">
-        <v>1</v>
+      <c r="F25" s="10" t="n">
+        <v>1.2</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-3.0</t>
+          <t>ratio=1.25 (n=2)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1272,12 +1270,12 @@
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1304,8 +1302,8 @@
       <c r="E27" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F27" s="10" t="n">
-        <v>5.2</v>
+      <c r="F27" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1314,7 +1312,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>3.0-7.0</t>
+          <t>ratio=1.00 (0.75-1.50)</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1341,8 +1339,8 @@
       <c r="E28" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>2</v>
+      <c r="F28" s="9" t="n">
+        <v>3.7</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1351,7 +1349,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>1.0-6.0</t>
+          <t>ratio=0.73 (0.62-1.00)</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1393,17 +1391,15 @@
         </is>
       </c>
       <c r="E30" s="8" t="n"/>
-      <c r="F30" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1430,8 +1426,8 @@
       <c r="E31" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F31" s="10" t="n">
-        <v>2</v>
+      <c r="F31" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1440,7 +1436,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.50 (1.00-3.00)</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1467,8 +1463,8 @@
       <c r="E32" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="10" t="n">
-        <v>1.5</v>
+      <c r="F32" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1477,7 +1473,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>1.0-7.0</t>
+          <t>ratio=1.00 (0.50-1.33)</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1504,8 +1500,8 @@
       <c r="E33" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>3.5</v>
+      <c r="F33" s="9" t="n">
+        <v>4.9</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1514,7 +1510,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>3.0-4.0</t>
+          <t>ratio=0.81 (0.42-1.00)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1558,17 +1554,17 @@
       <c r="E35" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F35" s="11" t="n">
-        <v>1</v>
+      <c r="F35" s="9" t="n">
+        <v>2.5</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.25 (1.00-3.00)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1595,17 +1591,17 @@
       <c r="E36" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="11" t="n">
+      <c r="F36" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1632,17 +1628,17 @@
       <c r="E37" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F37" s="11" t="n">
-        <v>1</v>
+      <c r="F37" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (0.67-1.00)</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1687,12 +1683,12 @@
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1719,8 +1715,8 @@
       <c r="E40" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F40" s="10" t="n">
-        <v>4</v>
+      <c r="F40" s="9" t="n">
+        <v>3.6</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1729,7 +1725,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>3.0-6.0</t>
+          <t>ratio=0.90 (0.38-1.00)</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1754,17 +1750,15 @@
         </is>
       </c>
       <c r="E41" s="8" t="n"/>
-      <c r="F41" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1791,8 +1785,8 @@
       <c r="E42" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F42" s="10" t="n">
-        <v>6</v>
+      <c r="F42" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1801,7 +1795,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>3.0-11.0</t>
+          <t>ratio=1.00 (0.75-2.25)</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1828,8 +1822,8 @@
       <c r="E43" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F43" s="11" t="n">
-        <v>6</v>
+      <c r="F43" s="10" t="n">
+        <v>2.9</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1838,7 +1832,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>6.0-6.0</t>
+          <t>ratio=0.57 (n=1)</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1865,8 +1859,8 @@
       <c r="E44" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F44" s="10" t="n">
-        <v>3.5</v>
+      <c r="F44" s="9" t="n">
+        <v>6.3</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1875,7 +1869,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>2.0-6.5</t>
+          <t>ratio=1.27 (1.23-1.60)</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1902,17 +1896,17 @@
       <c r="E45" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="11" t="n">
-        <v>1.5</v>
+      <c r="F45" s="9" t="n">
+        <v>1.2</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.25 (1.00-3.00)</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1956,17 +1950,17 @@
       <c r="E47" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="F47" s="9" t="n">
-        <v>24</v>
+      <c r="F47" s="10" t="n">
+        <v>3.8</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-129.8</t>
+          <t>ratio=0.54 (n=2)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -1993,8 +1987,8 @@
       <c r="E48" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F48" s="10" t="n">
-        <v>6</v>
+      <c r="F48" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -2003,7 +1997,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>3.5-7.0</t>
+          <t>ratio=0.83 (0.40-0.88)</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2030,8 +2024,8 @@
       <c r="E49" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F49" s="10" t="n">
-        <v>5</v>
+      <c r="F49" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -2040,7 +2034,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>3.0-9.0</t>
+          <t>ratio=1.00 (0.36-1.33)</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2067,8 +2061,8 @@
       <c r="E50" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F50" s="10" t="n">
-        <v>7.8</v>
+      <c r="F50" s="9" t="n">
+        <v>5.8</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2077,7 +2071,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>5.5-9.5</t>
+          <t>ratio=0.58 (0.40-1.00)</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2104,17 +2098,17 @@
       <c r="E51" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F51" s="9" t="n">
-        <v>6</v>
+      <c r="F51" s="10" t="n">
+        <v>2.3</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-77.5</t>
+          <t>ratio=0.77 (n=2)</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2141,7 +2135,7 @@
       <c r="E52" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="10" t="n">
+      <c r="F52" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
@@ -2151,7 +2145,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>0.5-2.0</t>
+          <t>ratio=1.00 (0.25-2.00)</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2195,8 +2189,8 @@
       <c r="E54" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="9" t="n">
-        <v>1.5</v>
+      <c r="F54" s="11" t="n">
+        <v>0.9</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2205,7 +2199,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-25.0</t>
+          <t>wc_ratio=0.88</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2230,17 +2224,15 @@
         </is>
       </c>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2268,12 +2260,12 @@
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2318,16 +2310,16 @@
         <v>1</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>1.0-5.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2354,8 +2346,8 @@
       <c r="E59" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F59" s="10" t="n">
-        <v>5.5</v>
+      <c r="F59" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2364,7 +2356,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>3.0-12.0</t>
+          <t>ratio=1.50 (0.50-1.73)</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2392,12 +2384,12 @@
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2425,12 +2417,12 @@
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2457,8 +2449,8 @@
       <c r="E62" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F62" s="10" t="n">
-        <v>7.8</v>
+      <c r="F62" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
@@ -2467,7 +2459,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>5.0-10.0</t>
+          <t>ratio=1.00 (0.50-1.71)</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2495,12 +2487,12 @@
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2544,8 +2536,8 @@
       <c r="E65" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F65" s="10" t="n">
-        <v>3</v>
+      <c r="F65" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2554,7 +2546,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>2.0-8.0</t>
+          <t>ratio=2.00 (1.00-2.50)</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2582,12 +2574,12 @@
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2615,16 +2607,16 @@
         <v>1</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>2.5-4.0</t>
+          <t>ratio=3.12 (n=2)</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2638,7 +2630,7 @@
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>153.8</v>
+        <v>124.7</v>
       </c>
     </row>
   </sheetData>
@@ -2706,7 +2698,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-058, 23-059, 23-060, 25-113, 25-010</t>
+          <t>25-039, 24-006, 25-042, 25-088, 25-085</t>
         </is>
       </c>
     </row>
@@ -4341,35 +4333,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23-058</t>
+          <t>25-039</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23-059</t>
+          <t>24-006</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23-060</t>
+          <t>25-042</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-113</t>
+          <t>25-088</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-010</t>
+          <t>25-085</t>
         </is>
       </c>
     </row>
@@ -4424,23 +4416,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4458,19 +4446,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>23-058, 23-059, 23-060, 25-010, 25-113</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4484,7 +4468,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4493,12 +4477,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.0-3.5</t>
+          <t>ratio=1.08 (0.88-1.50)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4498,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4523,12 +4507,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3.0-6.0</t>
+          <t>ratio=1.17 (0.29-2.00)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -4544,21 +4528,21 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.5-1.5</t>
+          <t>ratio=0.78 (n=2)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-113, 23-060, 23-059, 23-058</t>
+          <t>25-085, 25-039</t>
         </is>
       </c>
     </row>
@@ -4578,17 +4562,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-113, 23-060, 23-059, 23-058</t>
+          <t>25-085, 25-039</t>
         </is>
       </c>
     </row>
@@ -4608,17 +4592,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>23-060, 23-059, 23-058</t>
+          <t>25-085, 25-039</t>
         </is>
       </c>
     </row>
@@ -4634,21 +4618,21 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.50 (n=2)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-113, 23-060, 23-059, 23-058</t>
+          <t>25-085, 25-039</t>
         </is>
       </c>
     </row>
@@ -4664,21 +4648,21 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.5-3.5</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-113, 23-060, 23-059, 23-058</t>
+          <t>25-085, 25-039</t>
         </is>
       </c>
     </row>
@@ -4694,21 +4678,21 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.0-7.5</t>
+          <t>ratio=1.19 (n=2)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-113, 23-060, 23-059, 23-058</t>
+          <t>25-085, 25-039</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4708,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4733,12 +4717,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7.0-9.0</t>
+          <t>ratio=1.00 (0.60-1.10)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -4754,21 +4738,21 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>global:0.8-39.0</t>
+          <t>ratio=0.75 (0.47-1.10)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-088, 25-085, 25-042, 25-039</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4768,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4793,12 +4777,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3.0-5.5</t>
+          <t>ratio=0.83 (0.58-1.10)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-113, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4807,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-085, 25-042, 25-039</t>
         </is>
       </c>
     </row>
@@ -4844,21 +4828,21 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>global:0.5-3.0</t>
+          <t>ratio=1.25 (n=2)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-042, 25-039</t>
         </is>
       </c>
     </row>
@@ -4878,19 +4862,15 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>23-058, 23-059, 23-060, 25-010, 25-113</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4904,7 +4884,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4913,12 +4893,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3.0-7.0</t>
+          <t>ratio=1.00 (0.75-1.50)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4914,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4943,12 +4923,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.0-6.0</t>
+          <t>ratio=0.73 (0.62-1.00)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -4964,23 +4944,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4994,7 +4970,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5003,12 +4979,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.50 (1.00-3.00)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5000,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5033,12 +5009,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.0-7.0</t>
+          <t>ratio=1.00 (0.50-1.33)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5030,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5063,12 +5039,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3.0-4.0</t>
+          <t>ratio=0.81 (0.42-1.00)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -5084,23 +5060,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5114,21 +5086,21 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.25 (1.00-3.00)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-113, 23-060</t>
+          <t>25-088, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -5148,17 +5120,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-113, 23-060</t>
+          <t>25-088, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -5174,21 +5146,21 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (0.67-1.00)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-113, 23-060</t>
+          <t>25-088, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -5208,19 +5180,15 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>23-060, 25-113</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5234,7 +5202,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5243,12 +5211,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.0-6.0</t>
+          <t>ratio=0.90 (0.38-1.00)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -5264,23 +5232,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5294,7 +5258,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5303,12 +5267,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3.0-11.0</t>
+          <t>ratio=1.00 (0.75-2.25)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5288,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5333,12 +5297,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6.0-6.0</t>
+          <t>ratio=0.57 (n=1)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>23-060</t>
+          <t>25-039</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5318,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5363,12 +5327,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2.0-6.5</t>
+          <t>ratio=1.27 (1.23-1.60)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>23-060, 23-059, 23-058</t>
+          <t>25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -5384,21 +5348,21 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.25 (1.00-3.00)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -5414,21 +5378,21 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>24</v>
+        <v>3.8</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>global:1.0-129.8</t>
+          <t>ratio=0.54 (n=2)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-085, 24-006</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5408,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5453,12 +5417,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3.5-7.0</t>
+          <t>ratio=0.83 (0.40-0.88)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-113, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5438,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5483,12 +5447,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>3.0-9.0</t>
+          <t>ratio=1.00 (0.36-1.33)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-010, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-085, 25-042, 25-039</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5468,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5513,12 +5477,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>5.5-9.5</t>
+          <t>ratio=0.58 (0.40-1.00)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-010, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-085, 25-042, 25-039</t>
         </is>
       </c>
     </row>
@@ -5534,21 +5498,21 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>global:1.0-77.5</t>
+          <t>ratio=0.77 (n=2)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-085, 25-039</t>
         </is>
       </c>
     </row>
@@ -5573,12 +5537,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.5-2.0</t>
+          <t>ratio=1.00 (0.25-2.00)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5558,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5603,12 +5567,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>global:0.5-25.0</t>
+          <t>wc_ratio=0.88</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5624,23 +5588,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5658,19 +5618,15 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>23-060, 25-113</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5684,21 +5640,21 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.0-5.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-042, 25-039</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5670,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5723,12 +5679,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.0-12.0</t>
+          <t>ratio=1.50 (0.50-1.73)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -5748,19 +5704,15 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>23-058, 23-059, 23-060, 25-010, 25-113</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5778,19 +5730,15 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>23-060, 25-113</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5804,7 +5752,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5813,12 +5761,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>5.0-10.0</t>
+          <t>ratio=1.00 (0.50-1.71)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -5838,19 +5786,15 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>23-058, 23-059, 23-060, 25-010, 25-113</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5864,7 +5808,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5873,12 +5817,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2.0-8.0</t>
+          <t>ratio=2.00 (1.00-2.50)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
         </is>
       </c>
     </row>
@@ -5898,19 +5842,15 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>23-058, 23-059, 23-060, 25-010, 25-113</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5924,21 +5864,21 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2.5-4.0</t>
+          <t>ratio=3.12 (n=2)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>25-113, 25-010, 23-060, 23-059, 23-058</t>
+          <t>25-085, 25-039</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-087 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-087 GENERATED BUILD PLAN.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -84,12 +84,6 @@
         <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,7 +117,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-039, 24-006, 25-042, 25-088, 25-085</t>
+          <t>25-039, 24-006, 25-042, 25-085, 23-034</t>
         </is>
       </c>
     </row>
@@ -758,7 +751,7 @@
         <v>7</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>8.199999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.29-2.00)</t>
+          <t>ratio=1.44 (0.29-2.00)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -1034,7 +1027,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1043,7 +1036,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.60-1.10)</t>
+          <t>ratio=1.06 (0.60-1.17)</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1071,7 +1064,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1080,7 +1073,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.47-1.10)</t>
+          <t>ratio=0.50 (0.47-1.10)</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1125,7 +1118,7 @@
         <v>5</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1134,7 +1127,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.58-1.10)</t>
+          <t>ratio=0.75 (0.50-1.10)</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1232,17 +1225,17 @@
       <c r="E25" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="10" t="n">
-        <v>1.2</v>
+      <c r="F25" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (n=2)</t>
+          <t>ratio=1.00 (1.00-1.50)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1340,7 +1333,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1349,7 +1342,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.73 (0.62-1.00)</t>
+          <t>ratio=0.80 (0.62-1.17)</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1555,7 +1548,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1564,7 +1557,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-3.00)</t>
+          <t>ratio=1.50 (1.00-3.00)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1860,7 +1853,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1869,7 +1862,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.27 (1.23-1.60)</t>
+          <t>ratio=1.25 (0.62-1.60)</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1897,7 +1890,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1906,7 +1899,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-3.00)</t>
+          <t>ratio=1.50 (1.00-3.00)</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -2025,7 +2018,7 @@
         <v>3</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -2034,7 +2027,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.36-1.33)</t>
+          <t>ratio=1.17 (0.36-2.33)</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2062,7 +2055,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2071,7 +2064,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.58 (0.40-1.00)</t>
+          <t>ratio=0.75 (0.40-1.25)</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2145,7 +2138,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.25-2.00)</t>
+          <t>ratio=1.00 (0.25-1.00)</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2189,17 +2182,17 @@
       <c r="E54" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="11" t="n">
-        <v>0.9</v>
+      <c r="F54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=0.88</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2309,17 +2302,17 @@
       <c r="E58" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F58" s="10" t="n">
+      <c r="F58" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>ratio=1.00 (0.50-1.50)</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2347,7 +2340,7 @@
         <v>8</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>12</v>
+        <v>9.1</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2356,7 +2349,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.50-1.73)</t>
+          <t>ratio=1.14 (0.50-1.73)</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2450,7 +2443,7 @@
         <v>10</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
@@ -2459,7 +2452,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.71)</t>
+          <t>ratio=1.12 (0.50-1.71)</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2630,7 +2623,7 @@
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>124.7</v>
+        <v>127.3</v>
       </c>
     </row>
   </sheetData>
@@ -2698,7 +2691,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-039, 24-006, 25-042, 25-088, 25-085</t>
+          <t>25-039, 24-006, 25-042, 25-085, 23-034</t>
         </is>
       </c>
     </row>
@@ -4354,14 +4347,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-088</t>
+          <t>25-085</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-085</t>
+          <t>23-034</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4475,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4498,7 +4491,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.199999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4507,12 +4500,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.29-2.00)</t>
+          <t>ratio=1.44 (0.29-2.00)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4701,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4717,12 +4710,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.60-1.10)</t>
+          <t>ratio=1.06 (0.60-1.17)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4731,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4747,12 +4740,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.47-1.10)</t>
+          <t>ratio=0.50 (0.47-1.10)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039</t>
+          <t>25-085, 25-042, 25-039</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4761,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4777,12 +4770,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.58-1.10)</t>
+          <t>ratio=0.75 (0.50-1.10)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4805,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039</t>
+          <t>25-085, 25-042, 25-039</t>
         </is>
       </c>
     </row>
@@ -4828,21 +4821,21 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=1.25 (n=2)</t>
+          <t>ratio=1.00 (1.00-1.50)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-042, 25-039</t>
+          <t>25-042, 25-039, 23-034</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4891,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4907,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4923,12 +4916,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ratio=0.73 (0.62-1.00)</t>
+          <t>ratio=0.80 (0.62-1.17)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4977,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5007,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5037,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5079,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5095,12 +5088,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-3.00)</t>
+          <t>ratio=1.50 (1.00-3.00)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-088, 25-042, 25-039, 24-006</t>
+          <t>25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5123,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-088, 25-042, 25-039, 24-006</t>
+          <t>25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5153,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-088, 25-042, 25-039, 24-006</t>
+          <t>25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5209,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5265,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5311,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5327,12 +5320,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=1.27 (1.23-1.60)</t>
+          <t>ratio=1.25 (0.62-1.60)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5341,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5357,12 +5350,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-3.00)</t>
+          <t>ratio=1.50 (1.00-3.00)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5415,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-088, 25-042, 25-039, 24-006</t>
+          <t>25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5431,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5447,12 +5440,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.36-1.33)</t>
+          <t>ratio=1.17 (0.36-2.33)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039</t>
+          <t>25-085, 25-042, 25-039, 23-034</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5461,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5477,12 +5470,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ratio=0.58 (0.40-1.00)</t>
+          <t>ratio=0.75 (0.40-1.25)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039</t>
+          <t>25-085, 25-042, 25-039, 23-034</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5530,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.25-2.00)</t>
+          <t>ratio=1.00 (0.25-1.00)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -5558,21 +5551,21 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>wc_ratio=0.88</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>23-034</t>
         </is>
       </c>
     </row>
@@ -5644,17 +5637,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>ratio=1.00 (0.50-1.50)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>25-042, 25-039</t>
+          <t>25-042, 25-039, 23-034</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5663,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>12</v>
+        <v>9.1</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5679,12 +5672,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.50-1.73)</t>
+          <t>ratio=1.14 (0.50-1.73)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5745,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5761,12 +5754,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.71)</t>
+          <t>ratio=1.12 (0.50-1.71)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5815,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>25-088, 25-085, 25-042, 25-039, 24-006</t>
+          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-087 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-087 GENERATED BUILD PLAN.xlsx
@@ -80,8 +80,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -536,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-039, 24-006, 25-042, 25-085, 23-034</t>
+          <t>25-039, 24-006, 25-085, 25-088, 25-042</t>
         </is>
       </c>
     </row>
@@ -631,12 +631,12 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -664,12 +664,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -714,7 +714,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.08 (0.88-1.50)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -751,7 +751,7 @@
         <v>7</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>10.1</v>
+        <v>8</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.44 (0.29-2.00)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -787,17 +787,17 @@
       <c r="E11" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="10" t="n">
-        <v>0.8</v>
+      <c r="F11" s="9" t="n">
+        <v>1.2</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.78 (n=2)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -824,17 +824,17 @@
       <c r="E12" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>1</v>
+      <c r="F12" s="9" t="n">
+        <v>0.7</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -861,17 +861,17 @@
       <c r="E13" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="10" t="n">
-        <v>1</v>
+      <c r="F13" s="9" t="n">
+        <v>0.6</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -898,17 +898,17 @@
       <c r="E14" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="10" t="n">
-        <v>1.5</v>
+      <c r="F14" s="9" t="n">
+        <v>0.8</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (n=2)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -935,17 +935,17 @@
       <c r="E15" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>2</v>
+      <c r="F15" s="9" t="n">
+        <v>1.9</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -972,17 +972,17 @@
       <c r="E16" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>2.4</v>
+      <c r="F16" s="9" t="n">
+        <v>1.5</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.19 (n=2)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1027,7 +1027,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.06 (0.60-1.17)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1064,7 +1064,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.50 (0.47-1.10)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1118,7 +1118,7 @@
         <v>5</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.50-1.10)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1172,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1226,7 +1226,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.50)</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1263,12 +1263,12 @@
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1296,7 +1296,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.50)</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1333,7 +1333,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.62-1.17)</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1387,12 +1387,12 @@
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1420,7 +1420,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-3.00)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1457,7 +1457,7 @@
         <v>2</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.33)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1494,7 +1494,7 @@
         <v>6</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.81 (0.42-1.00)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1548,7 +1548,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-3.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1585,7 +1585,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1622,7 +1622,7 @@
         <v>3</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-1.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1676,12 +1676,12 @@
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1709,7 +1709,7 @@
         <v>4</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.90 (0.38-1.00)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1746,12 +1746,12 @@
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1779,7 +1779,7 @@
         <v>3</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-2.25)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1815,17 +1815,17 @@
       <c r="E43" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F43" s="10" t="n">
-        <v>2.9</v>
+      <c r="F43" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.57 (n=1)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1853,7 +1853,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.62-1.60)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1889,17 +1889,17 @@
       <c r="E45" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="9" t="n">
-        <v>1.5</v>
+      <c r="F45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-3.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1943,17 +1943,17 @@
       <c r="E47" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="F47" s="10" t="n">
+      <c r="F47" s="9" t="n">
         <v>3.8</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.54 (n=2)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -1981,7 +1981,7 @@
         <v>6</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.40-0.88)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2018,7 +2018,7 @@
         <v>3</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.36-2.33)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2055,7 +2055,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>7.5</v>
+        <v>4.7</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.40-1.25)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2091,17 +2091,17 @@
       <c r="E51" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F51" s="10" t="n">
-        <v>2.3</v>
+      <c r="F51" s="9" t="n">
+        <v>1.4</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.77 (n=2)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2129,7 +2129,7 @@
         <v>1</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.25-1.00)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2182,17 +2182,17 @@
       <c r="E54" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="10" t="n">
-        <v>1</v>
+      <c r="F54" s="9" t="n">
+        <v>0.5</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2220,12 +2220,12 @@
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2253,12 +2253,12 @@
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2303,7 +2303,7 @@
         <v>1</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.50)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2340,7 +2340,7 @@
         <v>8</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.14 (0.50-1.73)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2377,12 +2377,12 @@
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2410,12 +2410,12 @@
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2443,7 +2443,7 @@
         <v>10</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.12 (0.50-1.71)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2480,12 +2480,12 @@
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2530,7 +2530,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (1.00-2.50)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2567,12 +2567,12 @@
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2599,17 +2599,17 @@
       <c r="E67" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F67" s="10" t="n">
-        <v>3.1</v>
+      <c r="F67" s="9" t="n">
+        <v>2.9</v>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.12 (n=2)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>127.3</v>
+        <v>104.1</v>
       </c>
     </row>
   </sheetData>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-039, 24-006, 25-042, 25-085, 23-034</t>
+          <t>25-039, 24-006, 25-085, 25-088, 25-042</t>
         </is>
       </c>
     </row>
@@ -4340,21 +4340,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-042</t>
+          <t>25-085</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-085</t>
+          <t>25-088</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23-034</t>
+          <t>25-042</t>
         </is>
       </c>
     </row>
@@ -4413,15 +4413,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4439,15 +4443,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4461,7 +4469,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4470,12 +4478,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=1.08 (0.88-1.50)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4499,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10.1</v>
+        <v>8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4500,12 +4508,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=1.44 (0.29-2.00)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4521,21 +4529,21 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=0.78 (n=2)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-085, 25-039</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4551,21 +4559,21 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-085, 25-039</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4581,21 +4589,21 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-085, 25-039</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4611,21 +4619,21 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.50 (n=2)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-085, 25-039</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4641,21 +4649,21 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-085, 25-039</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4671,21 +4679,21 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=1.19 (n=2)</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-085, 25-039</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4709,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4710,12 +4718,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=1.06 (0.60-1.17)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4739,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4740,12 +4748,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=0.50 (0.47-1.10)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4769,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4770,12 +4778,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.50-1.10)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>model(SUPPORTS)</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4799,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4800,12 +4808,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4829,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4830,12 +4838,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.50)</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-042, 25-039, 23-034</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -4855,15 +4863,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4877,7 +4889,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4886,12 +4898,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.50)</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4919,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4916,12 +4928,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.62-1.17)</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -4941,15 +4953,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4963,7 +4979,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4972,12 +4988,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-3.00)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4993,7 +5009,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5002,12 +5018,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.33)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5039,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5032,12 +5048,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=0.81 (0.42-1.00)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5057,15 +5073,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5079,7 +5099,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5088,12 +5108,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-3.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-042, 25-039, 24-006, 23-034</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5129,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5118,12 +5138,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-042, 25-039, 24-006, 23-034</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5159,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5148,12 +5168,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-1.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-042, 25-039, 24-006, 23-034</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5173,15 +5193,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5195,7 +5219,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5204,12 +5228,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ratio=0.90 (0.38-1.00)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5229,15 +5253,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5251,7 +5279,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5260,12 +5288,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-2.25)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5281,21 +5309,21 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ratio=0.57 (n=1)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-039</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5339,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5320,12 +5348,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.62-1.60)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5341,21 +5369,21 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-3.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -5375,17 +5403,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ratio=0.54 (n=2)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-085, 24-006</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5429,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5410,12 +5438,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.40-0.88)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-042, 25-039, 24-006, 23-034</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5459,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5440,12 +5468,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.36-2.33)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 23-034</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5489,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7.5</v>
+        <v>4.7</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5470,12 +5498,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.40-1.25)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 23-034</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5491,21 +5519,21 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ratio=0.77 (n=2)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>25-085, 25-039</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5549,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5530,12 +5558,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.25-1.00)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5551,21 +5579,21 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:18h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>23-034</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -5585,15 +5613,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5611,15 +5643,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5633,7 +5669,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5642,12 +5678,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.50)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>25-042, 25-039, 23-034</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5699,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5672,12 +5708,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ratio=1.14 (0.50-1.73)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -5697,15 +5733,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5723,15 +5763,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5745,7 +5789,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5754,12 +5798,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ratio=1.12 (0.50-1.71)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -5779,15 +5823,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5801,7 +5849,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5810,12 +5858,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ratio=2.00 (1.00-2.50)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>25-085, 25-042, 25-039, 24-006, 23-034</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -5835,15 +5883,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5857,21 +5909,21 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ratio=3.12 (n=2)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>25-085, 25-039</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-087 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-087 GENERATED BUILD PLAN.xlsx
@@ -714,7 +714,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>7</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>5</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1172,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>group_total:6h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1296,7 +1296,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>group_total:6h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1333,7 +1333,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>group_total:6h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1548,7 +1548,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>3</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>4</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>7</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -1981,7 +1981,7 @@
         <v>6</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2018,7 +2018,7 @@
         <v>3</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2055,7 +2055,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2092,7 +2092,7 @@
         <v>3</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2303,7 +2303,7 @@
         <v>1</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2340,7 +2340,7 @@
         <v>8</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2443,7 +2443,7 @@
         <v>10</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>104.1</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>group_total:6h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>group_total:6h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>group_total:6h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5099,7 +5099,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>group_total:18h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
